--- a/РАБОЧИЙ СТОЛ/машины ПОКОМ ЗПФ.xlsx
+++ b/РАБОЧИЙ СТОЛ/машины ПОКОМ ЗПФ.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\РАБОЧИЙ СТОЛ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FF67A7-31E2-43A4-AEFA-9DCB37683337}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28ECB9C4-9E09-40DD-B16C-E485F843DAA9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,31 +66,31 @@
     <t>нетто</t>
   </si>
   <si>
-    <t>паллеты</t>
-  </si>
-  <si>
-    <t>Аист</t>
-  </si>
-  <si>
     <t>Владстандарт</t>
   </si>
   <si>
-    <t>Горняк</t>
-  </si>
-  <si>
     <t>ПРС ЛП</t>
   </si>
   <si>
     <t>Остаток, вес</t>
   </si>
   <si>
-    <t>Остаток, пал.</t>
-  </si>
-  <si>
-    <t>КОЛ-ВО ПАЛЛЕТ</t>
-  </si>
-  <si>
     <t>4 машина</t>
+  </si>
+  <si>
+    <t>КОЛ-ВО коробок</t>
+  </si>
+  <si>
+    <t>Горняк Донецк</t>
+  </si>
+  <si>
+    <t>коробок</t>
+  </si>
+  <si>
+    <t>Остаток, кор.</t>
+  </si>
+  <si>
+    <t>Горняк Луганск</t>
   </si>
 </sst>
 </file>
@@ -141,7 +141,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="35">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -585,19 +585,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -611,7 +598,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -641,16 +628,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -986,68 +972,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="47" t="s">
+      <c r="B1" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="49"/>
+      <c r="F1" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="49"/>
+      <c r="H1" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="49"/>
+      <c r="J1" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="50"/>
+      <c r="L1" s="42" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="38" t="s">
         <v>18</v>
-      </c>
-      <c r="D1" s="49" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="50"/>
-      <c r="F1" s="49" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="50"/>
-      <c r="H1" s="49" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="50"/>
-      <c r="J1" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="51"/>
-      <c r="L1" s="43" t="s">
-        <v>16</v>
-      </c>
-      <c r="M1" s="39" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="46"/>
-      <c r="B2" s="48"/>
-      <c r="C2" s="42"/>
+      <c r="A2" s="45"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="41"/>
       <c r="D2" s="8" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H2" s="8" t="s">
         <v>10</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="44"/>
-      <c r="M2" s="40"/>
+      <c r="K2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="43"/>
+      <c r="M2" s="39"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
@@ -1142,8 +1128,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
+      <c r="A7" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="10"/>
@@ -1166,7 +1152,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="14"/>
@@ -1189,7 +1175,7 @@
     </row>
     <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B9" s="25"/>
       <c r="C9" s="26"/>
@@ -1254,48 +1240,40 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L10" s="30">
+      <c r="L10" s="29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M10" s="31">
+      <c r="M10" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="35"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="37">
+      <c r="A11" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="32"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="31"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="M11" s="38">
+      <c r="M11" s="37">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="C12" s="27"/>
-      <c r="J12">
-        <f>SUM(J10:J11)</f>
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <f>SUM(K10:K11)</f>
-        <v>0</v>
-      </c>
       <c r="M12" s="27"/>
     </row>
   </sheetData>
